--- a/downloads/exportExelCustomerFilter5.xlsx
+++ b/downloads/exportExelCustomerFilter5.xlsx
@@ -40,7 +40,7 @@
     <t>individual</t>
   </si>
   <si>
-    <t>8000000015</t>
+    <t>9123456790</t>
   </si>
 </sst>
 </file>
